--- a/data/satisfaction_detail/2026/6月/特色美食廊.xlsx
+++ b/data/satisfaction_detail/2026/6月/特色美食廊.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.33</v>
+        <v>9.51</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>9.33</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>9.93</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,9 @@
           <t>园区停车方便</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
@@ -611,7 +613,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>9.93</v>
@@ -624,10 +626,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="15">
